--- a/resultados/urai/erros_varredura.xlsx
+++ b/resultados/urai/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F735"/>
+  <dimension ref="A1:F768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21000,6 +21000,930 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=10&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>0</v>
+      </c>
+      <c r="E736" t="n">
+        <v>6</v>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:52:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=10&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>0</v>
+      </c>
+      <c r="E737" t="n">
+        <v>6</v>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:52:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=11&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>0</v>
+      </c>
+      <c r="E738" t="n">
+        <v>6</v>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:52:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=11&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>0</v>
+      </c>
+      <c r="E739" t="n">
+        <v>6</v>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=12&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>0</v>
+      </c>
+      <c r="E740" t="n">
+        <v>6</v>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=12&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>0</v>
+      </c>
+      <c r="E741" t="n">
+        <v>6</v>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=13&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>0</v>
+      </c>
+      <c r="E742" t="n">
+        <v>6</v>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=13&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>0</v>
+      </c>
+      <c r="E743" t="n">
+        <v>6</v>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=37528008661605A6B890F7FFBDCBE1B2?d-5470-p=8&amp;6578706f7274=1&amp;formulario.exercicio=2021&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>0</v>
+      </c>
+      <c r="E744" t="n">
+        <v>6</v>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:18:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5E01D012A5937A08DE67316C899B0AF2?d-5470-p=7&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>400</v>
+      </c>
+      <c r="E745" t="n">
+        <v>6</v>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:44:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5E01D012A5937A08DE67316C899B0AF2?d-5470-p=7&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>0</v>
+      </c>
+      <c r="E746" t="n">
+        <v>6</v>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:44:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=63687EF061A9B26EA17196A7BBA62CB9?d-5470-p=8&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>0</v>
+      </c>
+      <c r="E747" t="n">
+        <v>6</v>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:45:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EDAED7803B3C3C5EB2815E70F28DF3FE?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>0</v>
+      </c>
+      <c r="E748" t="n">
+        <v>6</v>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EDAED7803B3C3C5EB2815E70F28DF3FE?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>400</v>
+      </c>
+      <c r="E749" t="n">
+        <v>6</v>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:48:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EDAED7803B3C3C5EB2815E70F28DF3FE?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>0</v>
+      </c>
+      <c r="E750" t="n">
+        <v>6</v>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:48:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E81B1087911344A3A1DA992D739E54F9?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=12&amp;formulario.mes=MARCO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>0</v>
+      </c>
+      <c r="E751" t="n">
+        <v>6</v>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:06:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E81B1087911344A3A1DA992D739E54F9?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=12&amp;formulario.mes=MARCO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>0</v>
+      </c>
+      <c r="E752" t="n">
+        <v>6</v>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6FA27A18A11FFA49885A2672C270D91F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>0</v>
+      </c>
+      <c r="E753" t="n">
+        <v>6</v>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:06:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EF37DC8C4EEC2CAC2EB1D3111305CA52?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>0</v>
+      </c>
+      <c r="E754" t="n">
+        <v>6</v>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:11:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F9C18FD53ABC1575B5EBC1EB7D9B8D96?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>0</v>
+      </c>
+      <c r="E755" t="n">
+        <v>6</v>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:11:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F2A9BAB0A44666C169D5E792CCF436A1?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>0</v>
+      </c>
+      <c r="E756" t="n">
+        <v>6</v>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:11:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D3F3E72399EFCB5A4F170F7950DC9045?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>0</v>
+      </c>
+      <c r="E757" t="n">
+        <v>6</v>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:42:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E1A83C4A9D4A6856C6701FAA8AC8EC9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>0</v>
+      </c>
+      <c r="E758" t="n">
+        <v>6</v>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:48:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CF5BB62CBB0FD2F47A4B5E9B864A47D5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>0</v>
+      </c>
+      <c r="E759" t="n">
+        <v>6</v>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=565086279675C8E043406EC56A904D06?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>0</v>
+      </c>
+      <c r="E760" t="n">
+        <v>6</v>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CBD05DF5E2ACD659B88C33786758D859?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>0</v>
+      </c>
+      <c r="E761" t="n">
+        <v>6</v>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:29:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=968C83CA6310EA95D7ED3E406036DF68?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>0</v>
+      </c>
+      <c r="E762" t="n">
+        <v>6</v>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:45:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4740F50B4D99D24EEB0855D92611CECD?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>0</v>
+      </c>
+      <c r="E763" t="n">
+        <v>6</v>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EC5575C4D89E1DE0F6CB170A72DB263A?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2017&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>0</v>
+      </c>
+      <c r="E764" t="n">
+        <v>6</v>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:55:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D01CDFEE13CE2B473098F08B2B1B68FF?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2016&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>0</v>
+      </c>
+      <c r="E765" t="n">
+        <v>6</v>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:02:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=99A3B033EC8D7CB0A3A68BA47E51AEEE?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>0</v>
+      </c>
+      <c r="E766" t="n">
+        <v>6</v>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>2026-08-15 04:37:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D78270496672EA6908651A2B975AD2BE?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=446</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>0</v>
+      </c>
+      <c r="E767" t="n">
+        <v>7</v>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>2026-08-15 08:02:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>urai</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>https://urai.pr.gov.br/indexAjax.php?pag=T0RnPU9EZz1PVFU9T0RZPU56Yz1PR009T1RNPU9HRT1PV1E9T1dFPU9XUT1PVFk9T1dNPU56RT1ZVFE9WVRRPU9UUT1PVFE9TnpZPVlUUT1ZVE09WVdJPVlUaz1PV0U9WVdRPVlXRT1ZV1U9&amp;tipoRel=csv&amp;ano=2024&amp;ementa=&amp;numero=&amp;data=&amp;empresa=&amp;origem=&amp;situacao=&amp;designacao=</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>0</v>
+      </c>
+      <c r="E768" t="n">
+        <v>8</v>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:39:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/urai/erros_varredura.xlsx
+++ b/resultados/urai/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F768"/>
+  <dimension ref="A1:F739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10340,23 +10340,23 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos;jsessionid=C3856C011F9CAA213AA60397EC3F91E1?6578706f7274=1&amp;d-5470-e=9</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50002</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2026-08-03 19:26:00</t>
+          <t>2026-08-03 19:58:21</t>
         </is>
       </c>
     </row>
@@ -10368,23 +10368,23 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/menuCustomizavel/downloadDocumento?formulario.idAnexo=117</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50002</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-08-03 19:40:05</t>
+          <t>2026-08-03 19:58:24</t>
         </is>
       </c>
     </row>
@@ -10396,23 +10396,23 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/menuCustomizavel/downloadDocumento?formulario.idAnexo=119</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50019</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2026-08-03 19:40:57</t>
+          <t>2026-08-03 19:58:25</t>
         </is>
       </c>
     </row>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50002</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50019</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:21</t>
+          <t>2026-08-03 19:58:29</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50002</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50008</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:24</t>
+          <t>2026-08-03 19:58:29</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50019</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50008</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:25</t>
+          <t>2026-08-03 19:58:37</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50019</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50009</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:29</t>
+          <t>2026-08-03 19:58:37</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50008</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50009</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:29</t>
+          <t>2026-08-03 19:58:55</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50008</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50063</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:37</t>
+          <t>2026-08-03 19:58:55</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50009</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50063</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:37</t>
+          <t>2026-08-03 19:58:59</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50009</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50099</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:55</t>
+          <t>2026-08-03 19:58:59</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50063</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50099</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:55</t>
+          <t>2026-08-03 19:59:17</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50063</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50100</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:59</t>
+          <t>2026-08-03 19:59:18</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50099</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50100</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2026-08-03 19:58:59</t>
+          <t>2026-08-03 19:59:25</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50099</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50101</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:17</t>
+          <t>2026-08-03 19:59:25</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50100</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50101</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:18</t>
+          <t>2026-08-03 19:59:29</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50100</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50102</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:25</t>
+          <t>2026-08-03 19:59:30</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50101</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50102</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:25</t>
+          <t>2026-08-03 19:59:48</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50101</t>
+          <t>https://uraipr.equiplano.com.br:7446/planoInvestimentos</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:29</t>
+          <t>2026-08-03 19:59:48</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50102</t>
+          <t>https://uraipr.equiplano.com.br:7446/planoInvestimentos</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:30</t>
+          <t>2026-08-03 19:59:52</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50102</t>
+          <t>https://uraipr.equiplano.com.br:7446/ldoFisicoFinanceiro</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:48</t>
+          <t>2026-08-03 19:59:53</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/planoInvestimentos</t>
+          <t>https://uraipr.equiplano.com.br:7446/ldoFisicoFinanceiro</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:48</t>
+          <t>2026-08-03 19:59:57</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/planoInvestimentos</t>
+          <t>https://uraipr.equiplano.com.br:7446/ldoMetaPrioridade</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:52</t>
+          <t>2026-08-03 19:59:57</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/ldoFisicoFinanceiro</t>
+          <t>https://uraipr.equiplano.com.br:7446/ldoMetaPrioridade</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:53</t>
+          <t>2026-08-03 20:00:09</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/ldoFisicoFinanceiro</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoesPrevistoRealizado</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:57</t>
+          <t>2026-08-03 20:00:09</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/ldoMetaPrioridade</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoesPrevistoRealizado</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>2026-08-03 19:59:57</t>
+          <t>2026-08-03 20:00:13</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/ldoMetaPrioridade</t>
+          <t>https://uraipr.equiplano.com.br:7446/diagnosticoEAvaliacao</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:09</t>
+          <t>2026-08-03 20:00:13</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoesPrevistoRealizado</t>
+          <t>https://uraipr.equiplano.com.br:7446/diagnosticoEAvaliacao</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:09</t>
+          <t>2026-08-03 20:00:17</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoesPrevistoRealizado</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDaEstimativaDeReceita</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:13</t>
+          <t>2026-08-03 20:00:18</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/diagnosticoEAvaliacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDaEstimativaDeReceita</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:13</t>
+          <t>2026-08-03 20:00:22</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/diagnosticoEAvaliacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoInvestimentos</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:17</t>
+          <t>2026-08-03 20:00:23</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDaEstimativaDeReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoInvestimentos</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:18</t>
+          <t>2026-08-03 20:00:27</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDaEstimativaDeReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoAvaliacao</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:22</t>
+          <t>2026-08-03 20:00:27</t>
         </is>
       </c>
     </row>
@@ -11264,7 +11264,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoInvestimentos</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoAvaliacao</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:23</t>
+          <t>2026-08-03 20:00:32</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoInvestimentos</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoes</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:27</t>
+          <t>2026-08-03 20:00:32</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoAvaliacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoes</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:27</t>
+          <t>2026-08-03 20:00:36</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoPorProgramaDeGovernoAvaliacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDosObjetivosAcoes</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:32</t>
+          <t>2026-08-03 20:00:37</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoes</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDosObjetivosAcoes</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:32</t>
+          <t>2026-08-03 20:00:41</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDasAcoes</t>
+          <t>https://uraipr.equiplano.com.br:7446/sumarioGeral/sumario</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:36</t>
+          <t>2026-08-03 20:00:42</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDosObjetivosAcoes</t>
+          <t>https://uraipr.equiplano.com.br:7446/sumarioGeral/sumario</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:37</t>
+          <t>2026-08-03 20:00:46</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoDosObjetivosAcoes</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo01ReceitaDespesaPorCategorias/receitaDespesaPorCategoria</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:41</t>
+          <t>2026-08-03 20:00:46</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/sumarioGeral/sumario</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo01ReceitaDespesaPorCategorias/receitaDespesaPorCategoria</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:42</t>
+          <t>2026-08-03 20:00:50</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/sumarioGeral/sumario</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo02ReceitasPorCategoria/receitaPorCategoria</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:46</t>
+          <t>2026-08-03 20:00:51</t>
         </is>
       </c>
     </row>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo01ReceitaDespesaPorCategorias/receitaDespesaPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo02ReceitasPorCategoria/receitaPorCategoria</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:46</t>
+          <t>2026-08-03 20:00:55</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo01ReceitaDespesaPorCategorias/receitaDespesaPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo02DespesasPorCategoriaSecretarias/despesasPorCategoria</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:50</t>
+          <t>2026-08-03 20:00:55</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo02ReceitasPorCategoria/receitaPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo02DespesasPorCategoriaSecretarias/despesasPorCategoria</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:51</t>
+          <t>2026-08-03 20:00:59</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo02ReceitasPorCategoria/receitaPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo02DespesasPorCategoriaConsolidado/despesasPorCategoria</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:55</t>
+          <t>2026-08-03 20:01:00</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo02DespesasPorCategoriaSecretarias/despesasPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo06DespesasPorFuncoesDeGovernoSecretarias/despesasPorFuncoesDeGoverno</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:55</t>
+          <t>2026-08-03 20:01:34</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo02DespesasPorCategoriaSecretarias/despesasPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo06DespesasPorFuncoesDeGovernoSecretarias/despesasPorFuncoesDeGoverno</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>2026-08-03 20:00:59</t>
+          <t>2026-08-03 20:01:47</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo02DespesasPorCategoriaConsolidado/despesasPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo07DespesasPorProgramasdeGovernoProjetosAtividades/despesasPorProgramasdeGoverno</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-08-03 20:01:00</t>
+          <t>2026-08-03 20:01:47</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo06DespesasPorFuncoesDeGovernoSecretarias/despesasPorFuncoesDeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo07DespesasPorProgramasdeGovernoProjetosAtividades/despesasPorProgramasdeGoverno</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>2026-08-03 20:01:34</t>
+          <t>2026-08-03 20:01:54</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo06DespesasPorFuncoesDeGovernoSecretarias/despesasPorFuncoesDeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo08DespesasPorProgramasDeGovernoOrdinariosVinculados/despesasPorProgramasDeGoverno</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>2026-08-03 20:01:47</t>
+          <t>2026-08-03 20:01:54</t>
         </is>
       </c>
     </row>
@@ -11796,7 +11796,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo07DespesasPorProgramasdeGovernoProjetosAtividades/despesasPorProgramasdeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo08DespesasPorProgramasDeGovernoOrdinariosVinculados/despesasPorProgramasDeGoverno</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>2026-08-03 20:01:47</t>
+          <t>2026-08-03 20:02:27</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo07DespesasPorProgramasdeGovernoProjetosAtividades/despesasPorProgramasdeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo09DespesasPorSecretariasFuncoesDeGoverno/despesasPorSecretariasFuncoesDeGoverno</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>2026-08-03 20:01:54</t>
+          <t>2026-08-03 20:02:28</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo08DespesasPorProgramasDeGovernoOrdinariosVinculados/despesasPorProgramasDeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/anexo09DespesasPorSecretariasFuncoesDeGoverno/despesasPorSecretariasFuncoesDeGoverno</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-08-03 20:01:54</t>
+          <t>2026-08-03 20:02:40</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo08DespesasPorProgramasDeGovernoOrdinariosVinculados/despesasPorProgramasDeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/caracterizacaoDosObjetivos/caracterizacaoDosObjetivos</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:27</t>
+          <t>2026-08-03 20:02:40</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo09DespesasPorSecretariasFuncoesDeGoverno/despesasPorSecretariasFuncoesDeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/caracterizacaoDosObjetivos/caracterizacaoDosObjetivos</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:28</t>
+          <t>2026-08-03 20:02:44</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/anexo09DespesasPorSecretariasFuncoesDeGoverno/despesasPorSecretariasFuncoesDeGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/quadroDeDetalhamentoDaDespesaOrcamentaria/detalhamentoDaDespesaOrcamentaria</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:40</t>
+          <t>2026-08-03 20:02:45</t>
         </is>
       </c>
     </row>
@@ -11964,7 +11964,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/caracterizacaoDosObjetivos/caracterizacaoDosObjetivos</t>
+          <t>https://uraipr.equiplano.com.br:7446/quadroDeDetalhamentoDaDespesaOrcamentaria/detalhamentoDaDespesaOrcamentaria</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:40</t>
+          <t>2026-08-03 20:02:49</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/caracterizacaoDosObjetivos/caracterizacaoDosObjetivos</t>
+          <t>https://uraipr.equiplano.com.br:7446/riscoFiscal/riscoFiscal</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:44</t>
+          <t>2026-08-03 20:02:49</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/quadroDeDetalhamentoDaDespesaOrcamentaria/detalhamentoDaDespesaOrcamentaria</t>
+          <t>https://uraipr.equiplano.com.br:7446/riscoFiscal/riscoFiscal</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:45</t>
+          <t>2026-08-03 20:02:53</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/quadroDeDetalhamentoDaDespesaOrcamentaria/detalhamentoDaDespesaOrcamentaria</t>
+          <t>https://uraipr.equiplano.com.br:7446/metasAnuais/metasAnuais</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:49</t>
+          <t>2026-08-03 20:02:54</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/riscoFiscal/riscoFiscal</t>
+          <t>https://uraipr.equiplano.com.br:7446/metasAnuais/metasAnuais</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:49</t>
+          <t>2026-08-03 20:02:58</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/riscoFiscal/riscoFiscal</t>
+          <t>https://uraipr.equiplano.com.br:7446/cumprimentoMetasFiscais</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:53</t>
+          <t>2026-08-03 20:02:58</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/metasAnuais/metasAnuais</t>
+          <t>https://uraipr.equiplano.com.br:7446/cumprimentoMetasFiscais</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:54</t>
+          <t>2026-08-03 20:03:13</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/metasAnuais/metasAnuais</t>
+          <t>https://uraipr.equiplano.com.br:7446/metasFiscais/metasFiscais</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:58</t>
+          <t>2026-08-03 20:03:13</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cumprimentoMetasFiscais</t>
+          <t>https://uraipr.equiplano.com.br:7446/metasFiscais/metasFiscais</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>2026-08-03 20:02:58</t>
+          <t>2026-08-03 20:03:17</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cumprimentoMetasFiscais</t>
+          <t>https://uraipr.equiplano.com.br:7446/evolucaoPatrimonioLiquido/evolucaoPatrimonioLiquido</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:13</t>
+          <t>2026-08-03 20:03:17</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/metasFiscais/metasFiscais</t>
+          <t>https://uraipr.equiplano.com.br:7446/evolucaoPatrimonioLiquido/evolucaoPatrimonioLiquido</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:13</t>
+          <t>2026-08-03 20:03:21</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/metasFiscais/metasFiscais</t>
+          <t>https://uraipr.equiplano.com.br:7446/alienacaoBens/alienacaoBens</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:17</t>
+          <t>2026-08-03 20:03:22</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/evolucaoPatrimonioLiquido/evolucaoPatrimonioLiquido</t>
+          <t>https://uraipr.equiplano.com.br:7446/alienacaoBens/alienacaoBens</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:17</t>
+          <t>2026-08-03 20:03:26</t>
         </is>
       </c>
     </row>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/evolucaoPatrimonioLiquido/evolucaoPatrimonioLiquido</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasRpps/receitasDespesasRpps</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:21</t>
+          <t>2026-08-03 20:03:26</t>
         </is>
       </c>
     </row>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/alienacaoBens/alienacaoBens</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasRpps/receitasDespesasRpps</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:22</t>
+          <t>2026-08-03 20:03:43</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/alienacaoBens/alienacaoBens</t>
+          <t>https://uraipr.equiplano.com.br:7446/projecaoAtuarial/projecaoAtuarial</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:26</t>
+          <t>2026-08-03 20:03:43</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasRpps/receitasDespesasRpps</t>
+          <t>https://uraipr.equiplano.com.br:7446/projecaoAtuarial/projecaoAtuarial</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:26</t>
+          <t>2026-08-03 20:04:16</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasRpps/receitasDespesasRpps</t>
+          <t>https://uraipr.equiplano.com.br:7446/renunciaReceita/renunciaReceita</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:43</t>
+          <t>2026-08-03 20:04:17</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/projecaoAtuarial/projecaoAtuarial</t>
+          <t>https://uraipr.equiplano.com.br:7446/renunciaReceita/renunciaReceita</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>2026-08-03 20:03:43</t>
+          <t>2026-08-03 20:04:21</t>
         </is>
       </c>
     </row>
@@ -12496,7 +12496,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/projecaoAtuarial/projecaoAtuarial</t>
+          <t>https://uraipr.equiplano.com.br:7446/margemExpansaoDespesas</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:16</t>
+          <t>2026-08-03 20:04:21</t>
         </is>
       </c>
     </row>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/renunciaReceita/renunciaReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/margemExpansaoDespesas</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:17</t>
+          <t>2026-08-03 20:04:25</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/renunciaReceita/renunciaReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/projetosEmAndamento/projetosEmAndamento</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:21</t>
+          <t>2026-08-03 20:04:26</t>
         </is>
       </c>
     </row>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/margemExpansaoDespesas</t>
+          <t>https://uraipr.equiplano.com.br:7446/projetosEmAndamento/projetosEmAndamento</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:21</t>
+          <t>2026-08-03 20:04:30</t>
         </is>
       </c>
     </row>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/margemExpansaoDespesas</t>
+          <t>https://uraipr.equiplano.com.br:7446/evolucaoReceita/evolucaoReceita</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:25</t>
+          <t>2026-08-03 20:04:30</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/projetosEmAndamento/projetosEmAndamento</t>
+          <t>https://uraipr.equiplano.com.br:7446/evolucaoReceita/evolucaoReceita</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:26</t>
+          <t>2026-08-03 20:04:34</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/projetosEmAndamento/projetosEmAndamento</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceita</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:30</t>
+          <t>2026-08-03 20:04:34</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/evolucaoReceita/evolucaoReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceita</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:30</t>
+          <t>2026-08-03 20:04:38</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12720,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/evolucaoReceita/evolucaoReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceitaIntra</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:34</t>
+          <t>2026-08-03 20:04:39</t>
         </is>
       </c>
     </row>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceitaIntra</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:34</t>
+          <t>2026-08-03 20:04:43</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesa</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:38</t>
+          <t>2026-08-03 20:04:43</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceitaIntra</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesa</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:39</t>
+          <t>2026-08-03 20:04:47</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioReceitaIntra</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesaIntra</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:43</t>
+          <t>2026-08-03 20:04:47</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesaIntra</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:43</t>
+          <t>2026-08-03 20:04:51</t>
         </is>
       </c>
     </row>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaFuncao</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:47</t>
+          <t>2026-08-03 20:04:52</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesaIntra</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaFuncao</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:47</t>
+          <t>2026-08-03 20:04:56</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/balancoOrcamentarioDespesaIntra</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncao</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:51</t>
+          <t>2026-08-03 20:04:56</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncao</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:52</t>
+          <t>2026-08-03 20:05:00</t>
         </is>
       </c>
     </row>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncaoIntra</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:56</t>
+          <t>2026-08-03 20:05:00</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncaoIntra</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>2026-08-03 20:04:56</t>
+          <t>2026-08-03 20:05:04</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaCorrenteLiquida</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:00</t>
+          <t>2026-08-03 20:05:05</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncaoIntra</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaCorrenteLiquida</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:00</t>
+          <t>2026-08-03 20:05:09</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaFuncaoSubFuncaoIntra</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasPrevidenciarias</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:04</t>
+          <t>2026-08-03 20:05:09</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaCorrenteLiquida</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasPrevidenciarias</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:05</t>
+          <t>2026-08-03 20:05:13</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaCorrenteLiquida</t>
+          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimarioNominal</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:09</t>
+          <t>2026-08-03 20:05:13</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasPrevidenciarias</t>
+          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimarioNominal</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:09</t>
+          <t>2026-08-03 20:05:17</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitasDespesasPrevidenciarias</t>
+          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimario</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:13</t>
+          <t>2026-08-03 20:05:18</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimarioNominal</t>
+          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimario</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:13</t>
+          <t>2026-08-03 20:05:22</t>
         </is>
       </c>
     </row>
@@ -13280,7 +13280,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimarioNominal</t>
+          <t>https://uraipr.equiplano.com.br:7446/resultadoNominal</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:17</t>
+          <t>2026-08-03 20:05:22</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimario</t>
+          <t>https://uraipr.equiplano.com.br:7446/resultadoNominal</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:18</t>
+          <t>2026-08-03 20:05:26</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resultadoPrimario</t>
+          <t>https://uraipr.equiplano.com.br:7446/restosAPagar</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:22</t>
+          <t>2026-08-03 20:05:26</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resultadoNominal</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaManutencaoDesenvEnsino</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:22</t>
+          <t>2026-08-03 20:06:01</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resultadoNominal</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaManutencaoDesenvEnsino</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:26</t>
+          <t>2026-08-03 20:06:06</t>
         </is>
       </c>
     </row>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/restosAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaOperacaoCreditoDespesaCapital</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>2026-08-03 20:05:26</t>
+          <t>2026-08-03 20:06:06</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaManutencaoDesenvEnsino</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaOperacaoCreditoDespesaCapital</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:01</t>
+          <t>2026-08-03 20:06:13</t>
         </is>
       </c>
     </row>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaManutencaoDesenvEnsino</t>
+          <t>https://uraipr.equiplano.com.br:7446/projecaoRegimeServidores</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:06</t>
+          <t>2026-08-03 20:06:13</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaOperacaoCreditoDespesaCapital</t>
+          <t>https://uraipr.equiplano.com.br:7446/projecaoRegimeServidores</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:06</t>
+          <t>2026-08-03 20:06:18</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaOperacaoCreditoDespesaCapital</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaAlienacaoAplicacaoRecurso</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:13</t>
+          <t>2026-08-03 20:06:18</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/projecaoRegimeServidores</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaAcoesSaude</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:13</t>
+          <t>2026-08-03 20:06:52</t>
         </is>
       </c>
     </row>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/projecaoRegimeServidores</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaAcoesSaude</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:18</t>
+          <t>2026-08-03 20:06:59</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaAlienacaoAplicacaoRecurso</t>
+          <t>https://uraipr.equiplano.com.br:7446/parceriasPublicoPrivada</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:18</t>
+          <t>2026-08-03 20:07:00</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13644,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaAcoesSaude</t>
+          <t>https://uraipr.equiplano.com.br:7446/parceriasPublicoPrivada</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:52</t>
+          <t>2026-08-03 20:07:04</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaAcoesSaude</t>
+          <t>https://uraipr.equiplano.com.br:7446/resumoExecucaoOrcamentaria</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>2026-08-03 20:06:59</t>
+          <t>2026-08-03 20:07:04</t>
         </is>
       </c>
     </row>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/parceriasPublicoPrivada</t>
+          <t>https://uraipr.equiplano.com.br:7446/resumoExecucaoOrcamentaria</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:00</t>
+          <t>2026-08-03 20:07:08</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/parceriasPublicoPrivada</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaComPessoal</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:04</t>
+          <t>2026-08-03 20:07:08</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resumoExecucaoOrcamentaria</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaComPessoal</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:04</t>
+          <t>2026-08-03 20:07:12</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/resumoExecucaoOrcamentaria</t>
+          <t>https://uraipr.equiplano.com.br:7446/dividaConsolidadaLiquida</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:08</t>
+          <t>2026-08-03 20:07:13</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaComPessoal</t>
+          <t>https://uraipr.equiplano.com.br:7446/dividaConsolidadaLiquida</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:08</t>
+          <t>2026-08-03 20:07:17</t>
         </is>
       </c>
     </row>
@@ -13840,7 +13840,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaComPessoal</t>
+          <t>https://uraipr.equiplano.com.br:7446/garantiasContragarantiasValores</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:12</t>
+          <t>2026-08-03 20:07:17</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/dividaConsolidadaLiquida</t>
+          <t>https://uraipr.equiplano.com.br:7446/garantiasContragarantiasValores</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:13</t>
+          <t>2026-08-03 20:07:21</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/dividaConsolidadaLiquida</t>
+          <t>https://uraipr.equiplano.com.br:7446/operacoesCredito</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:17</t>
+          <t>2026-08-03 20:07:21</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13924,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/garantiasContragarantiasValores</t>
+          <t>https://uraipr.equiplano.com.br:7446/operacoesCredito</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:17</t>
+          <t>2026-08-03 20:07:25</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/garantiasContragarantiasValores</t>
+          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixaRestosAPagar</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:21</t>
+          <t>2026-08-03 20:07:25</t>
         </is>
       </c>
     </row>
@@ -13980,7 +13980,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/operacoesCredito</t>
+          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixaRestosAPagar</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:21</t>
+          <t>2026-08-03 20:07:30</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/operacoesCredito</t>
+          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixa</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:25</t>
+          <t>2026-08-03 20:07:30</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixaRestosAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixa</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:25</t>
+          <t>2026-08-03 20:07:34</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixaRestosAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoRestosAPagar</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:30</t>
+          <t>2026-08-03 20:07:34</t>
         </is>
       </c>
     </row>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixa</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoRestosAPagar</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:30</t>
+          <t>2026-08-03 20:07:38</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/disponibilidadeCaixa</t>
+          <t>https://uraipr.equiplano.com.br:7446/gestaoFiscal</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:34</t>
+          <t>2026-08-03 20:07:39</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoRestosAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/gestaoFiscal</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:34</t>
+          <t>2026-08-03 20:07:43</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoRestosAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo01ReceitasDespesasPorCategoriaEconomica</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:38</t>
+          <t>2026-08-03 20:07:43</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/gestaoFiscal</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo01ReceitasDespesasPorCategoriaEconomica</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:39</t>
+          <t>2026-08-03 20:07:47</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/gestaoFiscal</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02ReceitasPorCategoria</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:43</t>
+          <t>2026-08-03 20:07:47</t>
         </is>
       </c>
     </row>
@@ -14260,7 +14260,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo01ReceitasDespesasPorCategoriaEconomica</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02ReceitasPorCategoria</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:43</t>
+          <t>2026-08-03 20:07:51</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo01ReceitasDespesasPorCategoriaEconomica</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02DespesasPorCategoria</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:47</t>
+          <t>2026-08-03 20:07:52</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02ReceitasPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02DespesasPorCategoria</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:47</t>
+          <t>2026-08-03 20:07:56</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14344,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02ReceitasPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo04DespesasPorCategoriaConsolidacao</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:51</t>
+          <t>2026-08-03 20:07:56</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02DespesasPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo04DespesasPorCategoriaConsolidacao</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:52</t>
+          <t>2026-08-03 20:08:00</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14400,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo02DespesasPorCategoria</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo05DespesasPorFuncaoConsolidacao</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:56</t>
+          <t>2026-08-03 20:08:00</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo04DespesasPorCategoriaConsolidacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo05DespesasPorFuncaoConsolidacao</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>2026-08-03 20:07:56</t>
+          <t>2026-08-03 20:08:04</t>
         </is>
       </c>
     </row>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo04DespesasPorCategoriaConsolidacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo06DespesasPorFuncao</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:00</t>
+          <t>2026-08-03 20:08:05</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo05DespesasPorFuncaoConsolidacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo06DespesasPorFuncao</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:00</t>
+          <t>2026-08-03 20:08:23</t>
         </is>
       </c>
     </row>
@@ -14512,7 +14512,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo05DespesasPorFuncaoConsolidacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo07DespesasPorFuncaoSubfuncaoProgramasProjetoAtividades</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:04</t>
+          <t>2026-08-03 20:08:23</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo06DespesasPorFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo07DespesasPorFuncaoSubfuncaoProgramasProjetoAtividades</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:05</t>
+          <t>2026-08-03 20:08:27</t>
         </is>
       </c>
     </row>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo06DespesasPorFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo08DespesaProgramaDeTrabalhoDoGoverno</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:23</t>
+          <t>2026-08-03 20:08:28</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo07DespesasPorFuncaoSubfuncaoProgramasProjetoAtividades</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo08DespesaProgramaDeTrabalhoDoGoverno</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:23</t>
+          <t>2026-08-03 20:08:32</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo07DespesasPorFuncaoSubfuncaoProgramasProjetoAtividades</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo09DespesasPorOrgaoFuncao</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:27</t>
+          <t>2026-08-03 20:08:32</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo08DespesaProgramaDeTrabalhoDoGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo09DespesasPorOrgaoFuncao</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:28</t>
+          <t>2026-08-03 20:08:36</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo08DespesaProgramaDeTrabalhoDoGoverno</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo10ComparativoDaReceitaPrevistaComArrecadada</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:32</t>
+          <t>2026-08-03 20:08:36</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo09DespesasPorOrgaoFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo10ComparativoDaReceitaPrevistaComArrecadada</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:32</t>
+          <t>2026-08-03 20:08:41</t>
         </is>
       </c>
     </row>
@@ -14736,7 +14736,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo09DespesasPorOrgaoFuncao</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo11ComparativoDaDespesaAutorizadaComRealizada</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:36</t>
+          <t>2026-08-03 20:08:41</t>
         </is>
       </c>
     </row>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo10ComparativoDaReceitaPrevistaComArrecadada</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo11ComparativoDaDespesaAutorizadaComRealizada</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:36</t>
+          <t>2026-08-03 20:08:45</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo10ComparativoDaReceitaPrevistaComArrecadada</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo12BalancoOrcamentario</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:41</t>
+          <t>2026-08-03 20:08:45</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo11ComparativoDaDespesaAutorizadaComRealizada</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo12BalancoOrcamentario</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:41</t>
+          <t>2026-08-03 20:08:49</t>
         </is>
       </c>
     </row>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo11ComparativoDaDespesaAutorizadaComRealizada</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo13BalancoFinanceiro</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:45</t>
+          <t>2026-08-03 20:08:49</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo12BalancoOrcamentario</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo13BalancoFinanceiro</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:45</t>
+          <t>2026-08-03 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo12BalancoOrcamentario</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo14BalancoPatrimonial</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:49</t>
+          <t>2026-08-03 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo13BalancoFinanceiro</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo14BalancoPatrimonial</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:49</t>
+          <t>2026-08-03 20:08:58</t>
         </is>
       </c>
     </row>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo13BalancoFinanceiro</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo15DemonstracoesDasVariacoesPatrimoniais</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:53</t>
+          <t>2026-08-03 20:08:58</t>
         </is>
       </c>
     </row>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo14BalancoPatrimonial</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo15DemonstracoesDasVariacoesPatrimoniais</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:54</t>
+          <t>2026-08-03 20:09:02</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo14BalancoPatrimonial</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo16DemonstrativoDaDividaFundadaInterna</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:58</t>
+          <t>2026-08-03 20:09:02</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo15DemonstracoesDasVariacoesPatrimoniais</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo16DemonstrativoDaDividaFundadaInterna</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>2026-08-03 20:08:58</t>
+          <t>2026-08-03 20:09:06</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo15DemonstracoesDasVariacoesPatrimoniais</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo17DemonstracoesDaDividaFlutuante</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:02</t>
+          <t>2026-08-03 20:09:07</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo16DemonstrativoDaDividaFundadaInterna</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo17DemonstracoesDaDividaFlutuante</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:02</t>
+          <t>2026-08-03 20:09:11</t>
         </is>
       </c>
     </row>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo16DemonstrativoDaDividaFundadaInterna</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaDemonstracaoDosFluxosDeCaixa</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:06</t>
+          <t>2026-08-03 20:09:11</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo17DemonstracoesDaDividaFlutuante</t>
+          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaDemonstracaoDosFluxosDeCaixa</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:07</t>
+          <t>2026-08-03 20:09:15</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaAnexo17DemonstracoesDaDividaFlutuante</t>
+          <t>https://uraipr.equiplano.com.br:7446/execOrcDemMutacoesDoPatrimonioLiquido</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:11</t>
+          <t>2026-08-03 20:09:15</t>
         </is>
       </c>
     </row>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaDemonstracaoDosFluxosDeCaixa</t>
+          <t>https://uraipr.equiplano.com.br:7446/execOrcDemMutacoesDoPatrimonioLiquido</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:11</t>
+          <t>2026-08-03 20:09:46</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15240,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execucaoOrcamentariaDemonstracaoDosFluxosDeCaixa</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresPensionistas</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:15</t>
+          <t>2026-08-03 20:09:47</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execOrcDemMutacoesDoPatrimonioLiquido</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresPensionistas</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:15</t>
+          <t>2026-08-03 20:10:10</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/execOrcDemMutacoesDoPatrimonioLiquido</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresAtivos</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:46</t>
+          <t>2026-08-03 20:10:11</t>
         </is>
       </c>
     </row>
@@ -15324,7 +15324,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresPensionistas</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresAtivos</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>2026-08-03 20:09:47</t>
+          <t>2026-08-03 20:10:15</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresPensionistas</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresInativos</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:10</t>
+          <t>2026-08-03 20:10:15</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresAtivos</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresInativos</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:11</t>
+          <t>2026-08-03 20:10:20</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresAtivos</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalarios</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:15</t>
+          <t>2026-08-03 20:10:21</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresInativos</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalarios</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:15</t>
+          <t>2026-08-03 20:10:35</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresInativos</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalariosDetalhado</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:20</t>
+          <t>2026-08-03 20:10:35</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalarios</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalariosDetalhado</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:21</t>
+          <t>2026-08-03 20:10:47</t>
         </is>
       </c>
     </row>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalarios</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeSalarios</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:35</t>
+          <t>2026-08-03 20:10:48</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalariosDetalhado</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeSalarios</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:35</t>
+          <t>2026-08-03 20:10:52</t>
         </is>
       </c>
     </row>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeServidoresSalariosDetalhado</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncional</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:47</t>
+          <t>2026-08-03 20:10:52</t>
         </is>
       </c>
     </row>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeSalarios</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncional</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:48</t>
+          <t>2026-08-03 20:10:56</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelacaoDeSalarios</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalCedidoRecebido</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:52</t>
+          <t>2026-08-03 20:10:56</t>
         </is>
       </c>
     </row>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncional</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalCedidoRecebido</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:52</t>
+          <t>2026-08-03 20:11:00</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncional</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalComissionado</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:56</t>
+          <t>2026-08-03 20:11:01</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalCedidoRecebido</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalComissionado</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>2026-08-03 20:10:56</t>
+          <t>2026-08-03 20:11:12</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalCedidoRecebido</t>
+          <t>https://uraipr.equiplano.com.br:7446/relatorioQuadroCargo</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:00</t>
+          <t>2026-08-03 20:11:13</t>
         </is>
       </c>
     </row>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalComissionado</t>
+          <t>https://uraipr.equiplano.com.br:7446/relatorioQuadroCargo</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:01</t>
+          <t>2026-08-03 20:11:25</t>
         </is>
       </c>
     </row>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhRelatorioQuadroFuncionalComissionado</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhEmpenhosDiariasConcedidasRecursosHumanos</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:12</t>
+          <t>2026-08-03 20:11:25</t>
         </is>
       </c>
     </row>
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relatorioQuadroCargo</t>
+          <t>https://uraipr.equiplano.com.br:7446/srhEmpenhosDiariasConcedidasRecursosHumanos</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:13</t>
+          <t>2026-08-03 20:11:29</t>
         </is>
       </c>
     </row>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relatorioQuadroCargo</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaOrcamentaria</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:25</t>
+          <t>2026-08-03 20:11:29</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhEmpenhosDiariasConcedidasRecursosHumanos</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaOrcamentaria</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:25</t>
+          <t>2026-08-03 20:11:33</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/srhEmpenhosDiariasConcedidasRecursosHumanos</t>
+          <t>https://uraipr.equiplano.com.br:7446/empenhosPorClassificacao</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:29</t>
+          <t>2026-08-03 20:11:34</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaOrcamentaria</t>
+          <t>https://uraipr.equiplano.com.br:7446/empenhosPorClassificacao</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:29</t>
+          <t>2026-08-03 20:11:52</t>
         </is>
       </c>
     </row>
@@ -15968,7 +15968,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaOrcamentaria</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhada</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:33</t>
+          <t>2026-08-03 20:11:52</t>
         </is>
       </c>
     </row>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/empenhosPorClassificacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhada</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:34</t>
+          <t>2026-08-03 20:11:56</t>
         </is>
       </c>
     </row>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/empenhosPorClassificacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaCompraDireta</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:52</t>
+          <t>2026-08-03 20:11:57</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhada</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaCompraDireta</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:52</t>
+          <t>2026-08-03 20:12:01</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhada</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaLiquidada</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:56</t>
+          <t>2026-08-03 20:12:01</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaCompraDireta</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaLiquidada</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>2026-08-03 20:11:57</t>
+          <t>2026-08-03 20:12:05</t>
         </is>
       </c>
     </row>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaCompraDireta</t>
+          <t>https://uraipr.equiplano.com.br:7446/ordemCronologicaPag</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:01</t>
+          <t>2026-08-03 20:12:05</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaLiquidada</t>
+          <t>https://uraipr.equiplano.com.br:7446/ordemCronologicaPag</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:01</t>
+          <t>2026-08-03 20:12:19</t>
         </is>
       </c>
     </row>
@@ -16192,7 +16192,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaLiquidada</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaPaga</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:05</t>
+          <t>2026-08-03 20:12:19</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/ordemCronologicaPag</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaPaga</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:05</t>
+          <t>2026-08-03 20:12:30</t>
         </is>
       </c>
     </row>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/ordemCronologicaPag</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaAPagar</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:19</t>
+          <t>2026-08-03 20:12:30</t>
         </is>
       </c>
     </row>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaPaga</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaAPagar</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:19</t>
+          <t>2026-08-03 20:12:34</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaPaga</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaDeAdiantamento</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:30</t>
+          <t>2026-08-03 20:12:34</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaDeAdiantamento</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:30</t>
+          <t>2026-08-03 20:12:53</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16360,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaEmpenhadaAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/saldoCredoresAPagar</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:34</t>
+          <t>2026-08-03 20:12:54</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaDeAdiantamento</t>
+          <t>https://uraipr.equiplano.com.br:7446/saldoCredoresAPagar</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:34</t>
+          <t>2026-08-03 20:13:11</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaDeAdiantamento</t>
+          <t>https://uraipr.equiplano.com.br:7446/empenhosDiariasConcedidas</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:53</t>
+          <t>2026-08-03 20:13:11</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/saldoCredoresAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/empenhosDiariasConcedidas</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:54</t>
+          <t>2026-08-03 20:13:42</t>
         </is>
       </c>
     </row>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/saldoCredoresAPagar</t>
+          <t>https://uraipr.equiplano.com.br:7446/transferenciasVoluntarias</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:11</t>
+          <t>2026-08-03 20:13:43</t>
         </is>
       </c>
     </row>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/empenhosDiariasConcedidas</t>
+          <t>https://uraipr.equiplano.com.br:7446/transferenciasVoluntarias</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:11</t>
+          <t>2026-08-03 20:13:48</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/empenhosDiariasConcedidas</t>
+          <t>https://uraipr.equiplano.com.br:7446/transferenciasTerceiros</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:42</t>
+          <t>2026-08-03 20:13:48</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transferenciasVoluntarias</t>
+          <t>https://uraipr.equiplano.com.br:7446/transferenciasTerceiros</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:43</t>
+          <t>2026-08-03 20:13:53</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transferenciasVoluntarias</t>
+          <t>https://uraipr.equiplano.com.br:7446/pagamentos</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:48</t>
+          <t>2026-08-03 20:13:53</t>
         </is>
       </c>
     </row>
@@ -16612,7 +16612,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transferenciasTerceiros</t>
+          <t>https://uraipr.equiplano.com.br:7446/pagamentos</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:48</t>
+          <t>2026-08-03 20:14:01</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transferenciasTerceiros</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoDocumentosFiscais</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:53</t>
+          <t>2026-08-03 20:14:01</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/pagamentos</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoDocumentosFiscais</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>2026-08-03 20:13:53</t>
+          <t>2026-08-03 20:14:05</t>
         </is>
       </c>
     </row>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/pagamentos</t>
+          <t>https://uraipr.equiplano.com.br:7446/movimentacaoFinanceira</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:01</t>
+          <t>2026-08-03 20:14:05</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoDocumentosFiscais</t>
+          <t>https://uraipr.equiplano.com.br:7446/movimentacaoFinanceira</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:01</t>
+          <t>2026-08-03 20:14:35</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoDocumentosFiscais</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaArrecadada</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:05</t>
+          <t>2026-08-03 20:14:36</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/movimentacaoFinanceira</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaArrecadada</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:05</t>
+          <t>2026-08-03 20:14:40</t>
         </is>
       </c>
     </row>
@@ -16808,7 +16808,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/movimentacaoFinanceira</t>
+          <t>https://uraipr.equiplano.com.br:7446/extratoFornecedor</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:35</t>
+          <t>2026-08-03 20:14:40</t>
         </is>
       </c>
     </row>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaArrecadada</t>
+          <t>https://uraipr.equiplano.com.br:7446/extratoFornecedor</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:36</t>
+          <t>2026-08-03 20:14:45</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaArrecadada</t>
+          <t>https://uraipr.equiplano.com.br:7446/pagamentosFornecedor</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:40</t>
+          <t>2026-08-03 20:14:46</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/extratoFornecedor</t>
+          <t>https://uraipr.equiplano.com.br:7446/pagamentosFornecedor</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:40</t>
+          <t>2026-08-03 20:14:50</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/extratoFornecedor</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoContasBancarias</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:45</t>
+          <t>2026-08-03 20:14:50</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/pagamentosFornecedor</t>
+          <t>https://uraipr.equiplano.com.br:7446/demonstrativoContasBancarias</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -16964,7 +16964,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:46</t>
+          <t>2026-08-03 20:14:54</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/pagamentosFornecedor</t>
+          <t>https://uraipr.equiplano.com.br:7446/recursosRecebidosConveniosFederais</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -16992,7 +16992,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:50</t>
+          <t>2026-08-03 20:14:54</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoContasBancarias</t>
+          <t>https://uraipr.equiplano.com.br:7446/recursosRecebidosConveniosFederais</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:50</t>
+          <t>2026-08-03 20:14:58</t>
         </is>
       </c>
     </row>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/demonstrativoContasBancarias</t>
+          <t>https://uraipr.equiplano.com.br:7446/transfVolunContratosParcerias</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:54</t>
+          <t>2026-08-03 20:14:59</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/recursosRecebidosConveniosFederais</t>
+          <t>https://uraipr.equiplano.com.br:7446/transfVolunContratosParcerias</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:54</t>
+          <t>2026-08-03 20:15:03</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/recursosRecebidosConveniosFederais</t>
+          <t>https://uraipr.equiplano.com.br:7446/transferenciasFinanceirasEntes</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:58</t>
+          <t>2026-08-03 20:15:03</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transfVolunContratosParcerias</t>
+          <t>https://uraipr.equiplano.com.br:7446/transferenciasFinanceirasEntes</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>2026-08-03 20:14:59</t>
+          <t>2026-08-03 20:15:07</t>
         </is>
       </c>
     </row>
@@ -17144,7 +17144,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transfVolunContratosParcerias</t>
+          <t>https://uraipr.equiplano.com.br:7446/emendasParlamentares</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:03</t>
+          <t>2026-08-03 20:15:08</t>
         </is>
       </c>
     </row>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transferenciasFinanceirasEntes</t>
+          <t>https://uraipr.equiplano.com.br:7446/emendasParlamentares</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:03</t>
+          <t>2026-08-03 20:15:11</t>
         </is>
       </c>
     </row>
@@ -17200,7 +17200,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transferenciasFinanceirasEntes</t>
+          <t>https://uraipr.equiplano.com.br:7446/fornecedoresImpedidosLicitar</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:07</t>
+          <t>2026-08-03 20:15:12</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/emendasParlamentares</t>
+          <t>https://uraipr.equiplano.com.br:7446/fornecedoresImpedidosLicitar</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:08</t>
+          <t>2026-08-03 20:15:16</t>
         </is>
       </c>
     </row>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/emendasParlamentares</t>
+          <t>https://uraipr.equiplano.com.br:7446/atosContratuais</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:11</t>
+          <t>2026-08-03 20:15:16</t>
         </is>
       </c>
     </row>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/fornecedoresImpedidosLicitar</t>
+          <t>https://uraipr.equiplano.com.br:7446/atosContratuais</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:12</t>
+          <t>2026-08-03 20:15:20</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/fornecedoresImpedidosLicitar</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratos</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:16</t>
+          <t>2026-08-03 20:15:20</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/atosContratuais</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosContrato</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:16</t>
+          <t>2026-08-03 20:15:55</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/atosContratuais</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosContrato</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:20</t>
+          <t>2026-08-03 20:16:02</t>
         </is>
       </c>
     </row>
@@ -17396,7 +17396,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratos</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosData</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:20</t>
+          <t>2026-08-03 20:16:02</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosContrato</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosData</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>2026-08-03 20:15:55</t>
+          <t>2026-08-03 20:16:10</t>
         </is>
       </c>
     </row>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosContrato</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosFornecedor</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:02</t>
+          <t>2026-08-03 20:16:11</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosData</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosFornecedor</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -17496,7 +17496,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:02</t>
+          <t>2026-08-03 20:16:15</t>
         </is>
       </c>
     </row>
@@ -17508,7 +17508,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosData</t>
+          <t>https://uraipr.equiplano.com.br:7446/licitacaoAgenda</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:10</t>
+          <t>2026-08-03 20:16:15</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosFornecedor</t>
+          <t>https://uraipr.equiplano.com.br:7446/licitacoes</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:11</t>
+          <t>2026-08-03 20:16:49</t>
         </is>
       </c>
     </row>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosFornecedor</t>
+          <t>https://uraipr.equiplano.com.br:7446/licitacoes</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:15</t>
+          <t>2026-08-03 20:16:58</t>
         </is>
       </c>
     </row>
@@ -17592,7 +17592,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/licitacaoAgenda</t>
+          <t>https://uraipr.equiplano.com.br:7446/fiscaisContratos</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:15</t>
+          <t>2026-08-03 20:16:58</t>
         </is>
       </c>
     </row>
@@ -17620,7 +17620,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/licitacoes</t>
+          <t>https://uraipr.equiplano.com.br:7446/fiscaisContratos</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:49</t>
+          <t>2026-08-03 20:17:02</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/licitacoes</t>
+          <t>https://uraipr.equiplano.com.br:7446/requisicoesCompra</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:58</t>
+          <t>2026-08-03 20:17:02</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/fiscaisContratos</t>
+          <t>https://uraipr.equiplano.com.br:7446/requisicoesCompra</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2026-08-03 20:16:58</t>
+          <t>2026-08-03 20:17:06</t>
         </is>
       </c>
     </row>
@@ -17704,7 +17704,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/fiscaisContratos</t>
+          <t>https://uraipr.equiplano.com.br:7446/proposta</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:02</t>
+          <t>2026-08-03 20:17:06</t>
         </is>
       </c>
     </row>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/requisicoesCompra</t>
+          <t>https://uraipr.equiplano.com.br:7446/proposta</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:02</t>
+          <t>2026-08-03 20:17:20</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/requisicoesCompra</t>
+          <t>https://uraipr.equiplano.com.br:7446/cotacao</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:06</t>
+          <t>2026-08-03 20:17:21</t>
         </is>
       </c>
     </row>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/proposta</t>
+          <t>https://uraipr.equiplano.com.br:7446/cotacao</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:06</t>
+          <t>2026-08-03 20:17:30</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/proposta</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtoCotado</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:20</t>
+          <t>2026-08-03 20:17:30</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cotacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtoCotado</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:21</t>
+          <t>2026-08-03 20:17:51</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17872,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cotacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtoContratado</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:30</t>
+          <t>2026-08-03 20:17:51</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtoCotado</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtoContratado</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:30</t>
+          <t>2026-08-03 20:17:55</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtoCotado</t>
+          <t>https://uraipr.equiplano.com.br:7446/chamamentoPublico</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:51</t>
+          <t>2026-08-03 20:17:56</t>
         </is>
       </c>
     </row>
@@ -17956,7 +17956,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtoContratado</t>
+          <t>https://uraipr.equiplano.com.br:7446/chamamentoPublico</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:51</t>
+          <t>2026-08-03 20:17:59</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtoContratado</t>
+          <t>https://uraipr.equiplano.com.br:7446/contasContabeis</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:55</t>
+          <t>2026-08-03 20:18:00</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/chamamentoPublico</t>
+          <t>https://uraipr.equiplano.com.br:7446/contasContabeis</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:56</t>
+          <t>2026-08-03 20:18:04</t>
         </is>
       </c>
     </row>
@@ -18040,7 +18040,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/chamamentoPublico</t>
+          <t>https://uraipr.equiplano.com.br:7446/contasReceita</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>2026-08-03 20:17:59</t>
+          <t>2026-08-03 20:18:04</t>
         </is>
       </c>
     </row>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contasContabeis</t>
+          <t>https://uraipr.equiplano.com.br:7446/contasReceita</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:00</t>
+          <t>2026-08-03 20:18:08</t>
         </is>
       </c>
     </row>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contasContabeis</t>
+          <t>https://uraipr.equiplano.com.br:7446/naturezasDespesa</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:04</t>
+          <t>2026-08-03 20:18:08</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contasReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/naturezasDespesa</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:04</t>
+          <t>2026-08-03 20:18:12</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contasReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/leiAto</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:08</t>
+          <t>2026-08-03 20:18:12</t>
         </is>
       </c>
     </row>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/naturezasDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/leiAto</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:08</t>
+          <t>2026-08-03 20:18:16</t>
         </is>
       </c>
     </row>
@@ -18208,7 +18208,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/naturezasDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniais</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:12</t>
+          <t>2026-08-03 20:18:17</t>
         </is>
       </c>
     </row>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/leiAto</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniais</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:12</t>
+          <t>2026-08-03 20:18:20</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/leiAto</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisPorPeriodo</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:16</t>
+          <t>2026-08-03 20:18:21</t>
         </is>
       </c>
     </row>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniais</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisPorPeriodo</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:17</t>
+          <t>2026-08-03 20:18:25</t>
         </is>
       </c>
     </row>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniais</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisRecebidosBaixadosPorDoacao</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:20</t>
+          <t>2026-08-03 20:18:25</t>
         </is>
       </c>
     </row>
@@ -18348,7 +18348,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisPorPeriodo</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisRecebidosBaixadosPorDoacao</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:21</t>
+          <t>2026-08-03 20:18:29</t>
         </is>
       </c>
     </row>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisPorPeriodo</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensCedidos</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:25</t>
+          <t>2026-08-03 20:18:29</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisRecebidosBaixadosPorDoacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/bensCedidos</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -18420,7 +18420,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:25</t>
+          <t>2026-08-03 20:18:33</t>
         </is>
       </c>
     </row>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensPatrimoniaisRecebidosBaixadosPorDoacao</t>
+          <t>https://uraipr.equiplano.com.br:7446/relRenunciaDeReceitas</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:29</t>
+          <t>2026-08-03 20:18:33</t>
         </is>
       </c>
     </row>
@@ -18460,7 +18460,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensCedidos</t>
+          <t>https://uraipr.equiplano.com.br:7446/relRenunciaDeReceitas</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -18476,7 +18476,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:29</t>
+          <t>2026-08-03 20:18:37</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/bensCedidos</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoItensEmEstoque</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:33</t>
+          <t>2026-08-03 20:18:37</t>
         </is>
       </c>
     </row>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relRenunciaDeReceitas</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoItensEmEstoque</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:33</t>
+          <t>2026-08-03 20:18:41</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relRenunciaDeReceitas</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoSitPedProtocolados</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:37</t>
+          <t>2026-08-03 20:18:42</t>
         </is>
       </c>
     </row>
@@ -18572,7 +18572,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoItensEmEstoque</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoSitPedProtocolados</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:37</t>
+          <t>2026-08-03 20:18:45</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoItensEmEstoque</t>
+          <t>https://uraipr.equiplano.com.br:7446/inscritosDividaAtiva</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:41</t>
+          <t>2026-08-03 20:18:46</t>
         </is>
       </c>
     </row>
@@ -18628,7 +18628,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoSitPedProtocolados</t>
+          <t>https://uraipr.equiplano.com.br:7446/inscritosDividaAtiva</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:42</t>
+          <t>2026-08-03 20:18:50</t>
         </is>
       </c>
     </row>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoSitPedProtocolados</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoFrotaMunicipal</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:45</t>
+          <t>2026-08-03 20:18:50</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/inscritosDividaAtiva</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoFrotaMunicipal</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:46</t>
+          <t>2026-08-03 20:18:54</t>
         </is>
       </c>
     </row>
@@ -18712,7 +18712,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/inscritosDividaAtiva</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoAbastecimento</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:50</t>
+          <t>2026-08-03 20:18:54</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoFrotaMunicipal</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoAbastecimento</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:50</t>
+          <t>2026-08-03 20:18:58</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoFrotaMunicipal</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoObraIntervencao</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -18784,7 +18784,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:54</t>
+          <t>2026-08-03 20:18:59</t>
         </is>
       </c>
     </row>
@@ -18796,7 +18796,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoAbastecimento</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoObraIntervencao</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:54</t>
+          <t>2026-08-03 20:19:03</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoAbastecimento</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50103</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:58</t>
+          <t>2026-08-03 20:19:03</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoObraIntervencao</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50103</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>2026-08-03 20:18:59</t>
+          <t>2026-08-03 20:19:07</t>
         </is>
       </c>
     </row>
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoObraIntervencao</t>
+          <t>https://uraipr.equiplano.com.br:7446/dadosSobreCovid19</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:03</t>
+          <t>2026-08-03 20:19:07</t>
         </is>
       </c>
     </row>
@@ -18908,7 +18908,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50103</t>
+          <t>https://uraipr.equiplano.com.br:7446/dadosSobreCovid19</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:03</t>
+          <t>2026-08-03 20:19:11</t>
         </is>
       </c>
     </row>
@@ -18936,7 +18936,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50103</t>
+          <t>https://uraipr.equiplano.com.br:7446/publicacoesCovid19</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:07</t>
+          <t>2026-08-03 20:19:11</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/dadosSobreCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/publicacoesCovid19</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:07</t>
+          <t>2026-08-03 20:19:15</t>
         </is>
       </c>
     </row>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/dadosSobreCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaCovid19</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:11</t>
+          <t>2026-08-03 20:19:15</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/publicacoesCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaCovid19</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:11</t>
+          <t>2026-08-03 20:19:19</t>
         </is>
       </c>
     </row>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/publicacoesCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaCovid19</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -19064,7 +19064,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:15</t>
+          <t>2026-08-03 20:19:19</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/despesaCovid19</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:15</t>
+          <t>2026-08-03 20:19:30</t>
         </is>
       </c>
     </row>
@@ -19104,7 +19104,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaCovid19</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:19</t>
+          <t>2026-08-03 20:19:31</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19132,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaCovid19</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:19</t>
+          <t>2026-08-03 20:19:35</t>
         </is>
       </c>
     </row>
@@ -19160,7 +19160,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/despesaCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosContratoCovid19</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:30</t>
+          <t>2026-08-03 20:19:35</t>
         </is>
       </c>
     </row>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/contratosContratoCovid19</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:31</t>
+          <t>2026-08-03 20:19:39</t>
         </is>
       </c>
     </row>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/receitaDespesaCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/revisaoContratoCovid19</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:35</t>
+          <t>2026-08-03 20:19:39</t>
         </is>
       </c>
     </row>
@@ -19244,7 +19244,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosContratoCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/revisaoContratoCovid19</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -19260,7 +19260,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:35</t>
+          <t>2026-08-03 20:19:44</t>
         </is>
       </c>
     </row>
@@ -19272,7 +19272,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/contratosContratoCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/licitacoesCovid19</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:39</t>
+          <t>2026-08-03 20:19:45</t>
         </is>
       </c>
     </row>
@@ -19300,7 +19300,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/revisaoContratoCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/licitacoesCovid19</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:39</t>
+          <t>2026-08-03 20:19:48</t>
         </is>
       </c>
     </row>
@@ -19328,7 +19328,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/revisaoContratoCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoServidoresCovid19</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:44</t>
+          <t>2026-08-03 20:19:49</t>
         </is>
       </c>
     </row>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/licitacoesCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/relacaoServidoresCovid19</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:45</t>
+          <t>2026-08-03 20:19:52</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/licitacoesCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtoCovid</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:48</t>
+          <t>2026-08-03 20:19:53</t>
         </is>
       </c>
     </row>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoServidoresCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtoCovid</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:49</t>
+          <t>2026-08-03 20:20:06</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/relacaoServidoresCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtosAdquiridosCovid19</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:52</t>
+          <t>2026-08-03 20:20:06</t>
         </is>
       </c>
     </row>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtoCovid</t>
+          <t>https://uraipr.equiplano.com.br:7446/produtosAdquiridosCovid19</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-08-03 20:19:53</t>
+          <t>2026-08-03 20:20:27</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtoCovid</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoReceita</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:06</t>
+          <t>2026-08-03 20:20:27</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtosAdquiridosCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoReceita</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:06</t>
+          <t>2026-08-03 20:20:31</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/produtosAdquiridosCovid19</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoDespesa</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:27</t>
+          <t>2026-08-03 20:20:31</t>
         </is>
       </c>
     </row>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoDespesa</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:27</t>
+          <t>2026-08-03 20:20:42</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoReceita</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:31</t>
+          <t>2026-08-03 20:20:42</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoReceita</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:31</t>
+          <t>2026-08-03 20:20:46</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpOrcamentoDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoDespesa</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -19680,7 +19680,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:42</t>
+          <t>2026-08-03 20:20:46</t>
         </is>
       </c>
     </row>
@@ -19692,7 +19692,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoDespesa</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:42</t>
+          <t>2026-08-03 20:20:50</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoReceita</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50024</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:46</t>
+          <t>2026-08-03 20:20:50</t>
         </is>
       </c>
     </row>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50024</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:46</t>
+          <t>2026-08-03 20:20:54</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/cpExecucaoDespesa</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50053</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:50</t>
+          <t>2026-08-03 20:20:55</t>
         </is>
       </c>
     </row>
@@ -19804,7 +19804,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50024</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50053</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:50</t>
+          <t>2026-08-03 20:20:59</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50024</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50076</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:54</t>
+          <t>2026-08-03 20:20:59</t>
         </is>
       </c>
     </row>
@@ -19860,7 +19860,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50053</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50076</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:55</t>
+          <t>2026-08-03 20:21:03</t>
         </is>
       </c>
     </row>
@@ -19888,7 +19888,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50053</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50077</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:59</t>
+          <t>2026-08-03 20:21:03</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50076</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50077</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>2026-08-03 20:20:59</t>
+          <t>2026-08-03 20:21:14</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50076</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50078</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:03</t>
+          <t>2026-08-03 20:21:14</t>
         </is>
       </c>
     </row>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50077</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50078</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19988,7 +19988,7 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:03</t>
+          <t>2026-08-03 20:21:37</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50077</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50094</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:14</t>
+          <t>2026-08-03 20:21:37</t>
         </is>
       </c>
     </row>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50078</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50094</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:14</t>
+          <t>2026-08-03 20:21:42</t>
         </is>
       </c>
     </row>
@@ -20056,7 +20056,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50078</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50096</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:37</t>
+          <t>2026-08-03 20:21:43</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50094</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50096</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:37</t>
+          <t>2026-08-03 20:21:47</t>
         </is>
       </c>
     </row>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50094</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50097</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:42</t>
+          <t>2026-08-03 20:21:47</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50096</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50097</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:43</t>
+          <t>2026-08-03 20:21:51</t>
         </is>
       </c>
     </row>
@@ -20168,7 +20168,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50096</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50095</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:47</t>
+          <t>2026-08-03 20:21:51</t>
         </is>
       </c>
     </row>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50097</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50095</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:47</t>
+          <t>2026-08-03 20:22:23</t>
         </is>
       </c>
     </row>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50097</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50098</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:51</t>
+          <t>2026-08-03 20:22:23</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50095</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50098</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>2026-08-03 20:21:51</t>
+          <t>2026-08-03 20:22:27</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50095</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:23</t>
+          <t>2026-08-03 20:22:27</t>
         </is>
       </c>
     </row>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50098</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50026</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:23</t>
+          <t>2026-08-03 20:22:32</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50098</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50032</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:27</t>
+          <t>2026-08-03 20:22:32</t>
         </is>
       </c>
     </row>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50026</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50032</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -20380,7 +20380,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:27</t>
+          <t>2026-08-03 20:22:36</t>
         </is>
       </c>
     </row>
@@ -20392,7 +20392,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50026</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50082</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:32</t>
+          <t>2026-08-03 20:22:36</t>
         </is>
       </c>
     </row>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50032</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50082</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:32</t>
+          <t>2026-08-03 20:22:40</t>
         </is>
       </c>
     </row>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50032</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50036</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:36</t>
+          <t>2026-08-03 20:22:41</t>
         </is>
       </c>
     </row>
@@ -20476,7 +20476,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50082</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50036</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -20492,7 +20492,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:36</t>
+          <t>2026-08-03 20:22:45</t>
         </is>
       </c>
     </row>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50082</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50040</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -20520,7 +20520,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:40</t>
+          <t>2026-08-03 20:22:45</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50036</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50040</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:41</t>
+          <t>2026-08-03 20:22:49</t>
         </is>
       </c>
     </row>
@@ -20560,7 +20560,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50036</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50042</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:45</t>
+          <t>2026-08-03 20:22:49</t>
         </is>
       </c>
     </row>
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50040</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50042</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -20604,7 +20604,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:45</t>
+          <t>2026-08-03 20:22:54</t>
         </is>
       </c>
     </row>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50040</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50044</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:49</t>
+          <t>2026-08-03 20:22:54</t>
         </is>
       </c>
     </row>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50042</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50044</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:49</t>
+          <t>2026-08-03 20:23:16</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50042</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50046</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -20688,7 +20688,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:54</t>
+          <t>2026-08-03 20:23:16</t>
         </is>
       </c>
     </row>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50044</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50046</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>2026-08-03 20:22:54</t>
+          <t>2026-08-03 20:23:20</t>
         </is>
       </c>
     </row>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50044</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50105</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:16</t>
+          <t>2026-08-03 20:23:21</t>
         </is>
       </c>
     </row>
@@ -20756,7 +20756,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50046</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50105</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:16</t>
+          <t>2026-08-03 20:23:25</t>
         </is>
       </c>
     </row>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50046</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50062</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:20</t>
+          <t>2026-08-03 20:23:25</t>
         </is>
       </c>
     </row>
@@ -20812,7 +20812,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50105</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50062</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:21</t>
+          <t>2026-08-03 20:23:29</t>
         </is>
       </c>
     </row>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50105</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50080</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:25</t>
+          <t>2026-08-03 20:23:29</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50062</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50080</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:25</t>
+          <t>2026-08-03 20:23:41</t>
         </is>
       </c>
     </row>
@@ -20896,7 +20896,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50062</t>
+          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50081</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:29</t>
+          <t>2026-08-03 20:23:42</t>
         </is>
       </c>
     </row>
@@ -20924,23 +20924,23 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50080</t>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=10&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D733" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E733" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:29</t>
+          <t>2026-08-14 15:52:47</t>
         </is>
       </c>
     </row>
@@ -20952,23 +20952,23 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50080</t>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=11&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D734" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E734" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:41</t>
+          <t>2026-08-14 15:53:00</t>
         </is>
       </c>
     </row>
@@ -20980,23 +20980,23 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/menuCustomizavel?idAcao=50081</t>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=12&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D735" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E735" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>2026-08-03 20:23:42</t>
+          <t>2026-08-14 15:53:13</t>
         </is>
       </c>
     </row>
@@ -21008,12 +21008,12 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=10&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=13&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D736" t="n">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>2026-08-14 15:52:47</t>
+          <t>2026-08-14 15:53:26</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=10&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5E01D012A5937A08DE67316C899B0AF2?d-5470-p=7&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=446</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-14 15:52:47</t>
+          <t>2026-08-14 18:44:57</t>
         </is>
       </c>
     </row>
@@ -21064,12 +21064,12 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=11&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EDAED7803B3C3C5EB2815E70F28DF3FE?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=446</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D738" t="n">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>2026-08-14 15:52:59</t>
+          <t>2026-08-14 18:48:51</t>
         </is>
       </c>
     </row>
@@ -21092,7 +21092,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=11&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
+          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E81B1087911344A3A1DA992D739E54F9?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=12&amp;formulario.mes=MARCO&amp;formulario.codEntidade=446</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -21108,819 +21108,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>2026-08-14 15:53:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B740" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=12&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C740" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D740" t="n">
-        <v>0</v>
-      </c>
-      <c r="E740" t="n">
-        <v>6</v>
-      </c>
-      <c r="F740" t="inlineStr">
-        <is>
-          <t>2026-08-14 15:53:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B741" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=12&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C741" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D741" t="n">
-        <v>0</v>
-      </c>
-      <c r="E741" t="n">
-        <v>6</v>
-      </c>
-      <c r="F741" t="inlineStr">
-        <is>
-          <t>2026-08-14 15:53:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B742" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=13&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C742" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D742" t="n">
-        <v>0</v>
-      </c>
-      <c r="E742" t="n">
-        <v>6</v>
-      </c>
-      <c r="F742" t="inlineStr">
-        <is>
-          <t>2026-08-14 15:53:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B743" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=14CE2D7DC02F053EF1B1AB53D2EED7A8?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2022&amp;d-5470-e=13&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C743" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D743" t="n">
-        <v>0</v>
-      </c>
-      <c r="E743" t="n">
-        <v>6</v>
-      </c>
-      <c r="F743" t="inlineStr">
-        <is>
-          <t>2026-08-14 15:53:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B744" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=37528008661605A6B890F7FFBDCBE1B2?d-5470-p=8&amp;6578706f7274=1&amp;formulario.exercicio=2021&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C744" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
-        </is>
-      </c>
-      <c r="D744" t="n">
-        <v>0</v>
-      </c>
-      <c r="E744" t="n">
-        <v>6</v>
-      </c>
-      <c r="F744" t="inlineStr">
-        <is>
-          <t>2026-08-14 17:18:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B745" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5E01D012A5937A08DE67316C899B0AF2?d-5470-p=7&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C745" t="inlineStr">
-        <is>
-          <t>HTTP_400</t>
-        </is>
-      </c>
-      <c r="D745" t="n">
-        <v>400</v>
-      </c>
-      <c r="E745" t="n">
-        <v>6</v>
-      </c>
-      <c r="F745" t="inlineStr">
-        <is>
-          <t>2026-08-14 18:44:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B746" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5E01D012A5937A08DE67316C899B0AF2?d-5470-p=7&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C746" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D746" t="n">
-        <v>0</v>
-      </c>
-      <c r="E746" t="n">
-        <v>6</v>
-      </c>
-      <c r="F746" t="inlineStr">
-        <is>
-          <t>2026-08-14 18:44:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B747" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=63687EF061A9B26EA17196A7BBA62CB9?d-5470-p=8&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C747" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D747" t="n">
-        <v>0</v>
-      </c>
-      <c r="E747" t="n">
-        <v>6</v>
-      </c>
-      <c r="F747" t="inlineStr">
-        <is>
-          <t>2026-08-14 18:45:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B748" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EDAED7803B3C3C5EB2815E70F28DF3FE?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C748" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D748" t="n">
-        <v>0</v>
-      </c>
-      <c r="E748" t="n">
-        <v>6</v>
-      </c>
-      <c r="F748" t="inlineStr">
-        <is>
-          <t>2026-08-14 18:48:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B749" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EDAED7803B3C3C5EB2815E70F28DF3FE?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C749" t="inlineStr">
-        <is>
-          <t>HTTP_400</t>
-        </is>
-      </c>
-      <c r="D749" t="n">
-        <v>400</v>
-      </c>
-      <c r="E749" t="n">
-        <v>6</v>
-      </c>
-      <c r="F749" t="inlineStr">
-        <is>
-          <t>2026-08-14 18:48:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B750" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EDAED7803B3C3C5EB2815E70F28DF3FE?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D750" t="n">
-        <v>0</v>
-      </c>
-      <c r="E750" t="n">
-        <v>6</v>
-      </c>
-      <c r="F750" t="inlineStr">
-        <is>
-          <t>2026-08-14 18:48:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B751" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E81B1087911344A3A1DA992D739E54F9?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=12&amp;formulario.mes=MARCO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C751" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D751" t="n">
-        <v>0</v>
-      </c>
-      <c r="E751" t="n">
-        <v>6</v>
-      </c>
-      <c r="F751" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:06:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B752" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E81B1087911344A3A1DA992D739E54F9?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=12&amp;formulario.mes=MARCO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C752" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D752" t="n">
-        <v>0</v>
-      </c>
-      <c r="E752" t="n">
-        <v>6</v>
-      </c>
-      <c r="F752" t="inlineStr">
-        <is>
           <t>2026-08-14 19:06:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B753" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6FA27A18A11FFA49885A2672C270D91F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D753" t="n">
-        <v>0</v>
-      </c>
-      <c r="E753" t="n">
-        <v>6</v>
-      </c>
-      <c r="F753" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:06:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B754" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EF37DC8C4EEC2CAC2EB1D3111305CA52?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C754" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D754" t="n">
-        <v>0</v>
-      </c>
-      <c r="E754" t="n">
-        <v>6</v>
-      </c>
-      <c r="F754" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:11:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B755" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F9C18FD53ABC1575B5EBC1EB7D9B8D96?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C755" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
-        </is>
-      </c>
-      <c r="D755" t="n">
-        <v>0</v>
-      </c>
-      <c r="E755" t="n">
-        <v>6</v>
-      </c>
-      <c r="F755" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:11:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B756" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F2A9BAB0A44666C169D5E792CCF436A1?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C756" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D756" t="n">
-        <v>0</v>
-      </c>
-      <c r="E756" t="n">
-        <v>6</v>
-      </c>
-      <c r="F756" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:11:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B757" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D3F3E72399EFCB5A4F170F7950DC9045?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C757" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D757" t="n">
-        <v>0</v>
-      </c>
-      <c r="E757" t="n">
-        <v>6</v>
-      </c>
-      <c r="F757" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:42:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B758" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E1A83C4A9D4A6856C6701FAA8AC8EC9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C758" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
-        </is>
-      </c>
-      <c r="D758" t="n">
-        <v>0</v>
-      </c>
-      <c r="E758" t="n">
-        <v>6</v>
-      </c>
-      <c r="F758" t="inlineStr">
-        <is>
-          <t>2026-08-14 19:48:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B759" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CF5BB62CBB0FD2F47A4B5E9B864A47D5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C759" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
-        </is>
-      </c>
-      <c r="D759" t="n">
-        <v>0</v>
-      </c>
-      <c r="E759" t="n">
-        <v>6</v>
-      </c>
-      <c r="F759" t="inlineStr">
-        <is>
-          <t>2026-08-14 20:05:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B760" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=565086279675C8E043406EC56A904D06?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C760" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
-        </is>
-      </c>
-      <c r="D760" t="n">
-        <v>0</v>
-      </c>
-      <c r="E760" t="n">
-        <v>6</v>
-      </c>
-      <c r="F760" t="inlineStr">
-        <is>
-          <t>2026-08-14 20:14:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B761" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CBD05DF5E2ACD659B88C33786758D859?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C761" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D761" t="n">
-        <v>0</v>
-      </c>
-      <c r="E761" t="n">
-        <v>6</v>
-      </c>
-      <c r="F761" t="inlineStr">
-        <is>
-          <t>2026-08-14 20:29:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B762" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=968C83CA6310EA95D7ED3E406036DF68?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C762" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D762" t="n">
-        <v>0</v>
-      </c>
-      <c r="E762" t="n">
-        <v>6</v>
-      </c>
-      <c r="F762" t="inlineStr">
-        <is>
-          <t>2026-08-14 20:45:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B763" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4740F50B4D99D24EEB0855D92611CECD?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C763" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D763" t="n">
-        <v>0</v>
-      </c>
-      <c r="E763" t="n">
-        <v>6</v>
-      </c>
-      <c r="F763" t="inlineStr">
-        <is>
-          <t>2026-08-14 21:35:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B764" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EC5575C4D89E1DE0F6CB170A72DB263A?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2017&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C764" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
-        </is>
-      </c>
-      <c r="D764" t="n">
-        <v>0</v>
-      </c>
-      <c r="E764" t="n">
-        <v>6</v>
-      </c>
-      <c r="F764" t="inlineStr">
-        <is>
-          <t>2026-08-14 23:55:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B765" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D01CDFEE13CE2B473098F08B2B1B68FF?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2016&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C765" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
-        </is>
-      </c>
-      <c r="D765" t="n">
-        <v>0</v>
-      </c>
-      <c r="E765" t="n">
-        <v>6</v>
-      </c>
-      <c r="F765" t="inlineStr">
-        <is>
-          <t>2026-08-15 01:02:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B766" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=99A3B033EC8D7CB0A3A68BA47E51AEEE?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C766" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
-        </is>
-      </c>
-      <c r="D766" t="n">
-        <v>0</v>
-      </c>
-      <c r="E766" t="n">
-        <v>6</v>
-      </c>
-      <c r="F766" t="inlineStr">
-        <is>
-          <t>2026-08-15 04:37:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B767" t="inlineStr">
-        <is>
-          <t>https://uraipr.equiplano.com.br:7446/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D78270496672EA6908651A2B975AD2BE?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=446</t>
-        </is>
-      </c>
-      <c r="C767" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
-        </is>
-      </c>
-      <c r="D767" t="n">
-        <v>0</v>
-      </c>
-      <c r="E767" t="n">
-        <v>7</v>
-      </c>
-      <c r="F767" t="inlineStr">
-        <is>
-          <t>2026-08-15 08:02:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
-        <is>
-          <t>urai</t>
-        </is>
-      </c>
-      <c r="B768" t="inlineStr">
-        <is>
-          <t>https://urai.pr.gov.br/indexAjax.php?pag=T0RnPU9EZz1PVFU9T0RZPU56Yz1PR009T1RNPU9HRT1PV1E9T1dFPU9XUT1PVFk9T1dNPU56RT1ZVFE9WVRRPU9UUT1PVFE9TnpZPVlUUT1ZVE09WVdJPVlUaz1PV0U9WVdRPVlXRT1ZV1U9&amp;tipoRel=csv&amp;ano=2024&amp;ementa=&amp;numero=&amp;data=&amp;empresa=&amp;origem=&amp;situacao=&amp;designacao=</t>
-        </is>
-      </c>
-      <c r="C768" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
-        </is>
-      </c>
-      <c r="D768" t="n">
-        <v>0</v>
-      </c>
-      <c r="E768" t="n">
-        <v>8</v>
-      </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>2026-08-15 09:39:40</t>
         </is>
       </c>
     </row>
